--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_78_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_78_IN_Piura.xlsx
@@ -1806,7 +1806,7 @@
       </c>
       <c r="C10" s="31">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>84.43</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>13.8</v>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>1.71</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.06</v>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="B15" s="45">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>35.1</v>
       </c>
       <c r="C15" s="46">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="44" t="inlineStr">
         <is>
@@ -1948,11 +1948,11 @@
       </c>
       <c r="B16" s="48">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>34.4804</v>
       </c>
       <c r="C16" s="49">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>98.23</v>
       </c>
       <c r="D16" s="47" t="inlineStr">
         <is>
@@ -1973,11 +1973,11 @@
       </c>
       <c r="B17" s="48">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>0.6196</v>
       </c>
       <c r="C17" s="49">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>1.77</v>
       </c>
       <c r="D17" s="47" t="inlineStr">
         <is>
@@ -2152,11 +2152,11 @@
       </c>
       <c r="B28" s="22">
         <f>SUM(B25:B27)</f>
-        <v/>
+        <v>35.1157</v>
       </c>
       <c r="C28" s="23">
         <f>SUM(C25:C27)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
       <c r="E28" s="17" t="inlineStr"/>
@@ -2275,6 +2275,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2390,6 +2391,7 @@
       <c r="F12" s="17" t="inlineStr"/>
       <c r="G12" s="17" t="inlineStr"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
@@ -2434,6 +2436,7 @@
       <c r="G15" s="8" t="n"/>
       <c r="H15" s="8" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17" ht="132" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
@@ -2983,11 +2986,11 @@
       </c>
       <c r="B22" s="33">
         <f>SUM(B10:B21)</f>
-        <v/>
+        <v>853.87</v>
       </c>
       <c r="C22" s="23">
         <f>SUM(C10:C21)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
@@ -2997,19 +3000,19 @@
       <c r="E22" s="17" t="inlineStr"/>
       <c r="F22" s="17">
         <f>ROUND(AVERAGE(F10:F21),2)</f>
-        <v/>
+        <v>28.51</v>
       </c>
       <c r="G22" s="22">
         <f>ROUND(AVERAGE(G10:G21),4)</f>
-        <v/>
+        <v>0.5992</v>
       </c>
       <c r="H22" s="23">
         <f>ROUND(AVERAGE(H10:H21),2)</f>
-        <v/>
+        <v>71.82</v>
       </c>
       <c r="I22" s="23">
         <f>ROUND(AVERAGE(I10:I21),2)</f>
-        <v/>
+        <v>19.14</v>
       </c>
     </row>
     <row r="23"/>
